--- a/chromadb/docs/gradreqs_qnas.xlsx
+++ b/chromadb/docs/gradreqs_qnas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AF0748-7781-42BE-A7AD-579C0E212324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F75332-8A39-4D01-99A9-06B89A1AD756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C8CE0056-11EC-46B5-A795-A52A002C1149}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$1:$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$1:$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
   <si>
     <t>What are the requirements for graduating from high school?</t>
   </si>
@@ -275,6 +275,290 @@
   <si>
     <t>What's your Student ID ?</t>
   </si>
+  <si>
+    <t>What are the English courses I can take ?</t>
+  </si>
+  <si>
+    <t>23.03400 Advanced Composition
+23.06400 Literary Types &amp; Composition
+23.03800 AP Seminar, ELA
+23.06500 AP English Literature &amp; Composition
+23.04300 AP English Language/Composition
+23.06510 Pre-AP English I
+23.05100 American Literature/Composition
+23.06520 Pre-AP English II
+23.05200 British Literature &amp; Composition
+23.06600 Contemporary Literature &amp; Composition
+23.05300 AP English Language &amp; Comp/American Lit
+23.06700 Multicultural Literature &amp; Composition
+23.06100 Ninth Grade Literature &amp; Composition
+23.06800 IB English A Literature (SL or HL), Year One
+23.06120 IB English B (SL or HL), Year One
+23.06900 IB English A Literature (SL or HL), Year Two
+23.06130 IB English B (SL or HL), Year Two
+23.07300 IB English A Language &amp; Lit (SL or HL), Year One
+23.06140 Enhanced Literature &amp; Composition I
+23.07310 IB English A Language &amp; Lit (SL or HL), Year Two
+23.06160 Literature &amp; Composition I
+23.07320 IB Literature &amp; Performance (SL or HL), Year One
+23.06170 Literature &amp; Composition II
+23.07330 IB Literature &amp; Performance (SL or HL), Year Two
+23.06180 Literature &amp; Composition III
+23.07400 Cambridge Advanced English General Paper (AS Level)
+23.06190 Literature &amp; Composition IV
+23.07410 Cambridge Advanced English Language (AS Level)
+23.06200 Tenth Grade Literature &amp; Composition
+23.07420 Cambridge Advanced English Language (A Level)
+23.06300 World Literature &amp; Composition
+52.09200 Dramatic Writing (Film, Television, &amp; Theatre I)</t>
+  </si>
+  <si>
+    <t>What are the maths mathematics courses I can take ?</t>
+  </si>
+  <si>
+    <t>27.05220 IB Mathematical Studies, Year One
+27.08410 Precalculus
+27.05240 IB Mathematical Studies, Year Two
+27.08430 Advanced Financial Algebra
+27.05310 IB Math: Analysis &amp; Approaches SL, Year One
+27.08500 Advanced Mathematical Decision Making1
+27.05320 IB Math: Analysis &amp; Approaches SL, Year Two
+27.08530 Linear Algebra with Computer Science Applications
+27.05330 IB Math: Analysis &amp; Approaches HL, Year One
+27.08600 Mathematics of Industry &amp; Government1
+27.05340 IB Math: Analysis &amp; Approaches HL, Year Two
+27.08630 History of Mathematics
+27.05350 IB Math: Applications &amp; Interpret SL, Year One
+27.08800 Statistical Reasoning1
+27.05360 IB Math: Applications &amp; Interpret SL, Year Two
+27.08900 College Readiness Mathematics Capstone Course1
+27.05370 IB Math: Applications &amp; Interpret HL, Year One
+27.09110 Enhanced Algebra: Concepts &amp; Connections
+27.05380 IB Math: Applications &amp; Interpret HL, Year Two
+27.09310 Enhanced Adv Alg &amp; AP Precalc: Concepts &amp; Connections
+27.07200 AP Calculus AB
+27.09710 GSE Coordinate Algebra2
+27.07300 AP Calculus BC
+27.09720 GSE Analytic Geometry2
+27.07400 AP Statistics
+27.09730 GSE Advanced Algebra2
+27.07410 AP Precalculus
+27.09740 GSE Pre-Calculus2
+27.07520 Differential Equations
+27.09750 Accel GSE Coordinate Algebra/Analytic Geometry A2
+27.07700 Multivariable Calculus
+27.09760 Accel GSE Analytic Geometry B/Advanced Algebra2
+27.07800 Calculus
+27.09770 Accelerated GSE Pre-Calculus2
+27.07910 Advanced Finite Mathematics
+27.09900 GSE Algebra I2
+27.08000 Engineering Calculus
+27.09910 GSE Geometry2
+27.08110 Algebra: Concepts &amp; Connections
+27.09920 GSE Algebra II2
+27.08210 Geometry: Concepts &amp; Connections
+27.09940 GSE Accelerated Algebra I/Geometry A2
+27.08310 Advanced Algebra: Concepts &amp; Connections
+27.09950 GSE Accelerated Geometry B/Algebra II2</t>
+  </si>
+  <si>
+    <t>What are the science courses I can take ?</t>
+  </si>
+  <si>
+    <t>01.46100 General Horticulture &amp; Plant Science
+26.07100 Zoology
+02.42100 Animal Science Technology/Biotechnology
+26.07200 Entomology
+02.44100 Plant Science &amp; Biotechnology
+26.07300 Human Anatomy/Physiology
+02.46200 Poultry Science
+28.01910 Aerospace Science: Science of Flight
+03.41100 Natural Resources Management
+40.01100 Physical Science
+03.45100 Forest Science
+40.02100 Astronomy
+11.01600 AP Computer Science A
+40.04100 Meteorology
+11.01700 IB Computer Science (SL or HL), Year One
+40.05000 Pre-AP Chemistry
+11.01710 IB Computer Science (SL or HL), Year Two
+40.05100 Chemistry I
+11.01900 AP Computer Science Principles
+40.05200 Chemistry II
+11.42500 Web Development
+40.05300 AP Chemistry
+11.42700 Embedded Computing
+40.05500 IB Chemistry (SL or HL), Year One
+11.42900 Game Design: Animation &amp; Simulation
+40.05600 IB Chemistry (SL or HL), Year Two
+11.47100 Computer Science Principles
+40.05610 Cambridge Advanced Chemistry (AS Level)
+11.47200 Programming, Games, Apps &amp; Society
+40.05620 Cambridge Advanced Chemistry (A Level)
+20.41400 Food for Life
+40.05700 Organic Chemistry
+20.41810 Food Science
+40.05800 Biochemistry
+20.41710 Food &amp; Nutrition Through the Lifespan
+40.05900 Materials Chemistry
+21.45100 Energy &amp; Power Technology
+40.06300 Geology
+21.45300 Advanced AC &amp; DC Circuits
+40.06400 Earth Systems
+21.45700 Appropriate &amp; Alternative Energy Technologies
+40.07100 Oceanography
+25.44000 Essentials of Healthcare
+40.08100 Physics I
+25.44600 Sports Medicine
+40.08200 Physics II
+25.57000 Essentials of Biotechnology
+40.08310 AP Physics 1
+25.56900 Applications of Biotechnology
+40.08320 AP Physics 2
+26.01200 Biology I
+40.08410 AP Physics C: Mechanics
+26.01210 Pre-AP Biology
+40.08420 AP Physics C: Electricity &amp; Magnetism
+26.01300 Biology II
+40.08500 IB Physics (SL or HL), Year One
+26.01400 AP Biology
+40.08600 IB Physics (SL or HL), Year Two
+26.01500 Genetics
+40.08610 Cambridge Advanced Physics (A Level)
+26.01800 IB Biology (SL or HL), Year One
+40.08620 Cambridge Advanced Physics (AS Level)
+26.01900 IB Biology (SL or HL), Year Two
+40.08700 Environmental Physics
+26.02000 IB Sports, Exercise &amp; Health Science (SL or HL), Year One
+40.08800 Special Topics in Modern Physics
+26.02100 IB Sports, Exercise &amp; Health Science (SL or HL), Year Two
+40.08900 Advanced Physics Principles/Robotics
+26.03100 Botany
+40.09100 Advanced Scientific Internship
+26.05100 Microbiology
+40.09230 Scientific Research III
+26.06100 Ecology
+40.09240 Scientific Research IV
+26.06110 Environmental Science
+40.09300 Forensic Science
+26.06200 AP Environmental Science
+40.09400 Chemical &amp; Material Science Engineering
+26.06300 IB Environmental Systems (SL), Year One
+40.09500 IB Design Technology (SL or HL), Year One
+26.06310 IB Environmental Systems (SL), Year Two
+40.09600 IB Design Technology (SL or HL), Year Two
+26.06320 Cambridge Advanced Environmental Management
+40.09700 IB Marine Science (SL), Year One
+26.06400 Advanced Genetics/DNA Research
+40.09710 IB Marine Science (SL), Year Two
+26.06500 Epidemiology
+43.45200 Forensic Science &amp; Criminal Investigations</t>
+  </si>
+  <si>
+    <t>45.01980 Pre-AP World History &amp; Geography
+45.08100 United States History
+45.08110 AP World History: Modern
+45.08200 AP United States History
+45.08300 World History
+45.08700 IB History of the Americas (SL or HL), Year One
+45.07110 World Geography
+45.07700 AP Human Geography</t>
+  </si>
+  <si>
+    <t>What courses focus on world studies ?</t>
+  </si>
+  <si>
+    <t>45.01980 Pre-AP World History &amp; Geography
+45.08110 AP World History: Modern
+45.08300 World History
+45.07110 World Geography
+45.07700 AP Human Geography</t>
+  </si>
+  <si>
+    <t>What courses focus on US history ?</t>
+  </si>
+  <si>
+    <t>45.08100 United States History
+45.08200 AP United States History
+45.08700 IB History of the Americas (SL or HL), Year One</t>
+  </si>
+  <si>
+    <t>ADDITIONAL COURSES THAT SATISFY THE THIRD SOCIAL SCIENCE UNIT</t>
+  </si>
+  <si>
+    <t>45.01100 Comparative Religions
+45.06100 Personal Finance &amp; Economics (eff 22-23)
+45.01110 IB World Religions (SL), Year One
+45.06200 AP Macroeconomics
+45.01120 IB World Religions (SL), Year Two
+45.06300 AP Microeconomics
+45.01200 Current Issues
+45.06400 Comparative Political/Economic Systems
+45.01300 Technology &amp; Society
+45.06500 IB Economics (SL or HL), Year One
+45.01310 IB Info Tech in a Global Society (SL or HL), Year One
+45.06600 IB Economics (SL or HL), Year Two
+45.01320 IB Info Tech in a Global Society (SL or HL), Year Two
+45.07200 Asian Studies
+45.01400 The Humanities/Social Studies
+45.07300 Latin American Studies
+45.01500 Psychology
+45.07400 Middle Eastern Studies
+45.01600 AP Psychology
+45.07500 Sub-Saharan Studies
+45.01700 IB Psychology (SL or HL), Year One
+45.07600 Local Area Studies/Geography
+45.01710 IB Psychology (SL or HL), Year Two
+45.07700 AP Human Geography
+45.01800 IB Philosophy, Year One
+45.07800 IB Geography (SL or HL), Year One
+45.01810 IB Philosophy, Year Two
+45.07900 IB Geography (SL or HL), Year Two
+45.02100 Anthropology
+45.08120 U.S. History in Film
+45.02200 IB Social &amp; Cultural Anthropology (SL or HL), Year One
+45.08400 AP European History
+45.02300 IB Social &amp; Cultural Anthropology (SL or HL), Year Two
+45.08500 Georgia History
+45.03100 Sociology
+45.08600 Local Area Studies/History
+45.03200 Ethnic Studies
+45.08900 Modern U.S. Military History, 1918-present
+45.05200 AP Government/Politics: United States
+45.08910 Early U.S. Military History
+45.05300 AP Government/Politics: Comparative
+45.08920 Recent U.S. Presidents
+45.05500 Constitutional Theory
+45.08930 IB History of the Americas (SL or HL), Year Two
+45.05600 The Individual &amp; the Law
+45.09100 United States &amp; World Affairs
+45.05700 American Government/Civics
+45.09200 World Area Studies
+45.05800 Ethics &amp; the Law
+45.09310 IB Global Politics (SL or HL), Year One
+45.06100 Economics/Business/Free Enterprise (through 21-22)
+45.09320 IB Global Politics (SL or HL), Year Two</t>
+  </si>
+  <si>
+    <t>computer science courses that satisfy the foreign language/american sign language/computer science requirement</t>
+  </si>
+  <si>
+    <t>11.01600 AP Computer Science A
+11.42700 Embedded Computing
+11.01700 IB Computer Science (SL or HL), Year One
+11.42900 Game Design: Animation &amp; Simulation
+11.01710 IB Computer Science (SL or HL), Year Two
+11.47100 Computer Science Principles
+11.01900 AP Computer Science Principles
+11.47200 Programming, Games, Apps &amp; Society
+11.42500 Web Development</t>
+  </si>
+  <si>
+    <t>What are the social science courses I can take ?</t>
+  </si>
+  <si>
+    <t>What courses focus on world history ?</t>
+  </si>
 </sst>
 </file>
 
@@ -309,8 +593,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,10 +912,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D8F601-1B4E-472D-B7C9-F81C7CDDCFD1}">
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="68.453125" customWidth="1"/>
+    <col min="1" max="1" width="69.08984375" customWidth="1"/>
     <col min="2" max="2" width="62.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.08984375" bestFit="1" customWidth="1"/>
@@ -17342,38 +17629,83 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B16" r:id="rId1" display="https://fultonga.scriborder.com/" xr:uid="{33FDBACC-E7BC-4158-8487-D894C6A8BF2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/chromadb/docs/gradreqs_qnas.xlsx
+++ b/chromadb/docs/gradreqs_qnas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F75332-8A39-4D01-99A9-06B89A1AD756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D276617C-718D-4A63-86ED-DA5B4A3DDBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C8CE0056-11EC-46B5-A795-A52A002C1149}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$1:$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$1:$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
   <si>
     <t>What are the requirements for graduating from high school?</t>
   </si>
@@ -559,6 +559,21 @@
   <si>
     <t>What courses focus on world history ?</t>
   </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>AP classes are advanced courses that can help you prepare for college-level work. They are often more challenging, but they can improve your college applications and earn you college credit if you score well on the AP exams.</t>
+  </si>
+  <si>
+    <t>advanced courses</t>
+  </si>
+  <si>
+    <t>counselling</t>
+  </si>
+  <si>
+    <t>Sure, what do you want to know. You can ask things like bullying, FAFSA, SAT, ACT, college, etc.</t>
+  </si>
 </sst>
 </file>
 
@@ -912,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D8F601-1B4E-472D-B7C9-F81C7CDDCFD1}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="69.08984375" customWidth="1"/>
@@ -17623,81 +17638,105 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>80</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B44" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+    <row r="45" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+    <row r="46" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+    <row r="47" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+    <row r="48" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>97</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+    <row r="49" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>89</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+    <row r="50" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>98</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+    <row r="51" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>91</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+    <row r="52" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>93</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+    <row r="53" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>96</v>
       </c>
     </row>

--- a/chromadb/docs/gradreqs_qnas.xlsx
+++ b/chromadb/docs/gradreqs_qnas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D276617C-718D-4A63-86ED-DA5B4A3DDBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6A9EA2-3B98-499A-BFD6-0996A529D4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C8CE0056-11EC-46B5-A795-A52A002C1149}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$1:$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$1:$82</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
   <si>
     <t>What are the requirements for graduating from high school?</t>
   </si>
@@ -574,6 +574,36 @@
   <si>
     <t>Sure, what do you want to know. You can ask things like bullying, FAFSA, SAT, ACT, college, etc.</t>
   </si>
+  <si>
+    <t>What are the core subjects ?</t>
+  </si>
+  <si>
+    <t>English, Maths, Science &amp; Social Science are the core subjects.</t>
+  </si>
+  <si>
+    <t>How many English credits do I need to take ?</t>
+  </si>
+  <si>
+    <t>You need to complete 4 units/credits of English. Ask - "What are the English courses I can take ?" to get the list of all courses.</t>
+  </si>
+  <si>
+    <t>How many Maths mathematics credits do I need to take ?</t>
+  </si>
+  <si>
+    <t>How many Science credits do I need to take ?</t>
+  </si>
+  <si>
+    <t>How many Social Science credits do I need to take ?</t>
+  </si>
+  <si>
+    <t>You need to complete 4 units/credits of Maths. Ask - "What are the maths mathematics courses I can take ?" to get the list of all courses.</t>
+  </si>
+  <si>
+    <t>You need to complete 4 units/credits of Science. Ask - "What are the Science courses I can take ?" to get the list of all courses.</t>
+  </si>
+  <si>
+    <t>You need to complete 3 units/credits of Social Science. Ask - "What are the Social Science courses I can take ?" to get the list of all courses.</t>
+  </si>
 </sst>
 </file>
 
@@ -927,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D8F601-1B4E-472D-B7C9-F81C7CDDCFD1}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="69.08984375" customWidth="1"/>
@@ -17342,407 +17372,447 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>80</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B49" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+    <row r="50" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+    <row r="51" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>97</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>91</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>98</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+    <row r="58" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>95</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B16" r:id="rId1" display="https://fultonga.scriborder.com/" xr:uid="{33FDBACC-E7BC-4158-8487-D894C6A8BF2B}"/>
+    <hyperlink ref="B21" r:id="rId1" display="https://fultonga.scriborder.com/" xr:uid="{33FDBACC-E7BC-4158-8487-D894C6A8BF2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
